--- a/- D-Hash Values.xlsx
+++ b/- D-Hash Values.xlsx
@@ -8,13 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8820AC-993C-487E-B9A6-0D88929E6018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C489C2-9622-4C61-B279-07CE2BC32382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24150" yWindow="4905" windowWidth="15375" windowHeight="5835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Devices Database" sheetId="1" r:id="rId1"/>
+    <sheet name="DevicesDatabase" sheetId="1" r:id="rId1"/>
+    <sheet name="LennaDatabase" sheetId="2" r:id="rId2"/>
+    <sheet name="MountainDatabase" sheetId="5" r:id="rId3"/>
+    <sheet name="PalaceDatabase" sheetId="6" r:id="rId4"/>
+    <sheet name="WashingtonDatabase" sheetId="3" r:id="rId5"/>
+    <sheet name="ParkDatabase" sheetId="7" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LennaDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MountainDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PalaceDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="122">
   <si>
     <t>Original</t>
   </si>
@@ -70,14 +82,343 @@
   </si>
   <si>
     <t>d9d9d2d1d0d0f321</t>
+  </si>
+  <si>
+    <t>Blackberry (2)</t>
+  </si>
+  <si>
+    <t>6870d947e4ed41e5</t>
+  </si>
+  <si>
+    <t>31f216c4ee6363a2</t>
+  </si>
+  <si>
+    <t>Canon (2)</t>
+  </si>
+  <si>
+    <t>68f1b3cdc44dc185</t>
+  </si>
+  <si>
+    <t>Iphone (2)</t>
+  </si>
+  <si>
+    <t>78b052c4c9434763</t>
+  </si>
+  <si>
+    <t>Sony (2)</t>
+  </si>
+  <si>
+    <t>D.Hashing</t>
+  </si>
+  <si>
+    <t>Imagem Original</t>
+  </si>
+  <si>
+    <t>7670795b33135a38</t>
+  </si>
+  <si>
+    <t>Bordas Enfatizadas</t>
+  </si>
+  <si>
+    <t>6470795b33135a38</t>
+  </si>
+  <si>
+    <t>Filtro de Gaussiana3x3</t>
+  </si>
+  <si>
+    <t>Filtro de Gaussiana7x7</t>
+  </si>
+  <si>
+    <t>Adição de Texto</t>
+  </si>
+  <si>
+    <t>Imagem em Bmp</t>
+  </si>
+  <si>
+    <t>Imagem em Png</t>
+  </si>
+  <si>
+    <t>Imagem em Tiff</t>
+  </si>
+  <si>
+    <t>Pouca alteração</t>
+  </si>
+  <si>
+    <t>Muita alteração</t>
+  </si>
+  <si>
+    <t>7e30795b33135a38</t>
+  </si>
+  <si>
+    <t>Metade Alterada</t>
+  </si>
+  <si>
+    <t>7670795b12000000</t>
+  </si>
+  <si>
+    <t>Filtro de Média3x3</t>
+  </si>
+  <si>
+    <t>Filtro de Média7x7</t>
+  </si>
+  <si>
+    <t>Filtro de Mediana3x3</t>
+  </si>
+  <si>
+    <t>Filtro de Mediana7x7</t>
+  </si>
+  <si>
+    <t>Ruído Sal e Pimenta</t>
+  </si>
+  <si>
+    <t>7670795b33131a38</t>
+  </si>
+  <si>
+    <t>Binarização com OTSU</t>
+  </si>
+  <si>
+    <t>6474695b33131a38</t>
+  </si>
+  <si>
+    <t>Efeito Espelho</t>
+  </si>
+  <si>
+    <t>91f161253337a5e3</t>
+  </si>
+  <si>
+    <t>Escala de Cinza</t>
+  </si>
+  <si>
+    <t>Adição de Objetos</t>
+  </si>
+  <si>
+    <t>7431c9cb33135a38</t>
+  </si>
+  <si>
+    <t>Fig01_WashingtonDC_Band1</t>
+  </si>
+  <si>
+    <t>d3d85833daeab5a9</t>
+  </si>
+  <si>
+    <t>Fig02_WashingtonDC_Band2</t>
+  </si>
+  <si>
+    <t>d6d85a73f8a2b5a9</t>
+  </si>
+  <si>
+    <t>Fig03_WashingtonDC_Band3</t>
+  </si>
+  <si>
+    <t>d7d85a73f8a2b5a9</t>
+  </si>
+  <si>
+    <t>Fig04_WashingtonDC_Band4</t>
+  </si>
+  <si>
+    <t>2cad290c0f4f494d</t>
+  </si>
+  <si>
+    <t>Fig05_WashingtonDC_Band5</t>
+  </si>
+  <si>
+    <t>44dc79395bca8949</t>
+  </si>
+  <si>
+    <t>Fig06_WashingtonDC_Band6</t>
+  </si>
+  <si>
+    <t>d7d858315aeaa0a9</t>
+  </si>
+  <si>
+    <t>Fig07_WashingtonDC_Band7</t>
+  </si>
+  <si>
+    <t>d6d85833daea88a9</t>
+  </si>
+  <si>
+    <t>Lenna Database</t>
+  </si>
+  <si>
+    <t>402416531b191a1f</t>
+  </si>
+  <si>
+    <t>Mountain Database</t>
+  </si>
+  <si>
+    <t>402416531b191a1b</t>
+  </si>
+  <si>
+    <t>402416531b391a1b</t>
+  </si>
+  <si>
+    <t>002416531b399a3e</t>
+  </si>
+  <si>
+    <t>412416531b391a3f</t>
+  </si>
+  <si>
+    <t>002416531b391e3f</t>
+  </si>
+  <si>
+    <t>002436531b391a3f</t>
+  </si>
+  <si>
+    <t>002416531b399a3a</t>
+  </si>
+  <si>
+    <t>402416531b391a3f</t>
+  </si>
+  <si>
+    <t>Palace Database</t>
+  </si>
+  <si>
+    <t>e6ce8e991c149694</t>
+  </si>
+  <si>
+    <t>e6ce8e993c149694</t>
+  </si>
+  <si>
+    <t>e6ce8e9938149694</t>
+  </si>
+  <si>
+    <t>e6ce8e9918149694</t>
+  </si>
+  <si>
+    <t>e6ce8e891c149694</t>
+  </si>
+  <si>
+    <t>e6ce8e893c149694</t>
+  </si>
+  <si>
+    <t>e6ce8e8918149694</t>
+  </si>
+  <si>
+    <t>Alternative 01</t>
+  </si>
+  <si>
+    <t>Alternative 02</t>
+  </si>
+  <si>
+    <t>Alternative 03</t>
+  </si>
+  <si>
+    <t>Alternative 04</t>
+  </si>
+  <si>
+    <t>Alternative 05</t>
+  </si>
+  <si>
+    <t>Alternative 06</t>
+  </si>
+  <si>
+    <t>Alternative 07</t>
+  </si>
+  <si>
+    <t>Alternative 08</t>
+  </si>
+  <si>
+    <t>Alternative 09</t>
+  </si>
+  <si>
+    <t>Alternative 10</t>
+  </si>
+  <si>
+    <t>Alternative 11</t>
+  </si>
+  <si>
+    <t>Alternative 12</t>
+  </si>
+  <si>
+    <t>Alternative 13</t>
+  </si>
+  <si>
+    <t>Alternative 14</t>
+  </si>
+  <si>
+    <t>Alternative 15</t>
+  </si>
+  <si>
+    <t>Alternative 16</t>
+  </si>
+  <si>
+    <t>Alternative 17</t>
+  </si>
+  <si>
+    <t>Alternative 18</t>
+  </si>
+  <si>
+    <t>Alternative 19</t>
+  </si>
+  <si>
+    <t>Alternative 20</t>
+  </si>
+  <si>
+    <t>Alternative 21</t>
+  </si>
+  <si>
+    <t>Alternative 22</t>
+  </si>
+  <si>
+    <t>Alternative 23</t>
+  </si>
+  <si>
+    <t>Alternative 24</t>
+  </si>
+  <si>
+    <t>Alternative 25</t>
+  </si>
+  <si>
+    <t>Alternative 26</t>
+  </si>
+  <si>
+    <t>Alternative 27</t>
+  </si>
+  <si>
+    <t>Alternative 28</t>
+  </si>
+  <si>
+    <t>Alternative 29</t>
+  </si>
+  <si>
+    <t>Alternative 30</t>
+  </si>
+  <si>
+    <t>eecede9d3e7cb6b6</t>
+  </si>
+  <si>
+    <t>eecede9d3e7cb6b4</t>
+  </si>
+  <si>
+    <t>e6cece9d3c7cf6b6</t>
+  </si>
+  <si>
+    <t>e6cede9d3e7cf6b6</t>
+  </si>
+  <si>
+    <t>eecede9d3c7cf6b6</t>
+  </si>
+  <si>
+    <t>e6cedc9d3c7cb6b6</t>
+  </si>
+  <si>
+    <t>Park Database</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -91,15 +432,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,12 +460,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -402,63 +779,1035 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B035164-966C-4B99-9EC3-82759FDF3491}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/- D-Hash Values.xlsx
+++ b/- D-Hash Values.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C489C2-9622-4C61-B279-07CE2BC32382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF256C7-49D8-4666-ACA8-317AF96D4D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DevicesDatabase" sheetId="1" r:id="rId1"/>
-    <sheet name="LennaDatabase" sheetId="2" r:id="rId2"/>
-    <sheet name="MountainDatabase" sheetId="5" r:id="rId3"/>
-    <sheet name="PalaceDatabase" sheetId="6" r:id="rId4"/>
-    <sheet name="WashingtonDatabase" sheetId="3" r:id="rId5"/>
+    <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
+    <sheet name="WashingtonDatabase" sheetId="3" r:id="rId2"/>
+    <sheet name="PalaceDatabase" sheetId="6" r:id="rId3"/>
+    <sheet name="MountainDatabase" sheetId="5" r:id="rId4"/>
+    <sheet name="DevicesDatabase" sheetId="1" r:id="rId5"/>
     <sheet name="ParkDatabase" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LennaDatabase!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MountainDatabase!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PalaceDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
   <si>
     <t>Original</t>
   </si>
@@ -403,6 +403,18 @@
   </si>
   <si>
     <t>Park Database</t>
+  </si>
+  <si>
+    <t>4659d98bcbcb9639</t>
+  </si>
+  <si>
+    <t>4659d98bcbcb9e39</t>
+  </si>
+  <si>
+    <t>4659d98b8b8b9a39</t>
+  </si>
+  <si>
+    <t>4659d98b8b8b9839</t>
   </si>
 </sst>
 </file>
@@ -769,6 +781,812 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B035164-966C-4B99-9EC3-82759FDF3491}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -891,812 +1709,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B035164-966C-4B99-9EC3-82759FDF3491}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1723,7 +1735,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1731,7 +1743,7 @@
         <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1739,7 +1751,7 @@
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1747,7 +1759,7 @@
         <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1755,7 +1767,7 @@
         <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1763,7 +1775,7 @@
         <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1771,7 +1783,7 @@
         <v>90</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1779,7 +1791,7 @@
         <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1787,7 +1799,7 @@
         <v>92</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1795,7 +1807,7 @@
         <v>93</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1803,7 +1815,7 @@
         <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/- D-Hash Values.xlsx
+++ b/- D-Hash Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF256C7-49D8-4666-ACA8-317AF96D4D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0550AB9-118A-4F52-81D5-994A9660EF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="133">
   <si>
     <t>Original</t>
   </si>
@@ -415,6 +415,27 @@
   </si>
   <si>
     <t>4659d98b8b8b9839</t>
+  </si>
+  <si>
+    <t>HNN</t>
+  </si>
+  <si>
+    <t>Nok</t>
+  </si>
+  <si>
+    <t>467059531c111138</t>
+  </si>
+  <si>
+    <t>HNN Result</t>
+  </si>
+  <si>
+    <t>1 Entrada com 128 = Underfitting</t>
+  </si>
+  <si>
+    <t>+ 3 Entradas com 128 = Overfitting</t>
+  </si>
+  <si>
+    <t>2-3 Entradas com 128 = Ok</t>
   </si>
 </sst>
 </file>
@@ -491,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -502,6 +523,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,182 +806,257 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="F5" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/- D-Hash Values.xlsx
+++ b/- D-Hash Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0550AB9-118A-4F52-81D5-994A9660EF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679E111C-9C89-48F1-9217-66C044188657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
